--- a/docs/downloads/经营分_鲁东省区__临沂片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁东省区__临沂片区_2026-10-18.xlsx
@@ -955,33 +955,33 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>7289738256752347193</t>
+          <t>7624435828743211058</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（临沂罗庄区政府双月湖店）</t>
+          <t>希岸酒店（临沂商城会展中心汽车站店）</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(临沂罗庄区政府双月湖店)</t>
+          <t>希岸酒店(临沂商城会展中心汽车站店)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>90</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -991,19 +991,19 @@
         <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
         <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P5" t="n">
         <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R5" t="n">
         <v>30</v>
@@ -1043,29 +1043,29 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>7071840620058249219</t>
+          <t>7289738256752347193</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0临沂南坊琅琊古城奥体中心店）</t>
+          <t>维也纳3好酒店（临沂罗庄区政府双月湖店）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0临沂南坊琅琊古城奥体中心店)</t>
+          <t>维也纳3好酒店(临沂罗庄区政府双月湖店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>90</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1079,19 +1079,19 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
+        <v>25</v>
+      </c>
+      <c r="N6" t="n">
+        <v>30</v>
+      </c>
+      <c r="O6" t="n">
+        <v>20</v>
+      </c>
+      <c r="P6" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="n">
         <v>15</v>
-      </c>
-      <c r="N6" t="n">
-        <v>30</v>
-      </c>
-      <c r="O6" t="n">
-        <v>20</v>
-      </c>
-      <c r="P6" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>25</v>
       </c>
       <c r="R6" t="n">
         <v>30</v>
@@ -1131,17 +1131,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>6697091890640062471</t>
+          <t>7071840620058249219</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>维也纳酒店（临沂蒙阴店）</t>
+          <t>维也纳酒店（5.0临沂南坊琅琊古城奥体中心店）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>维也纳酒店(临沂蒙阴店)</t>
+          <t>维也纳酒店(5.0临沂南坊琅琊古城奥体中心店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="N7" t="n">
         <v>30</v>
@@ -1179,7 +1179,7 @@
         <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R7" t="n">
         <v>30</v>
@@ -1307,33 +1307,33 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7624435828743211058</t>
+          <t>7094979881469118501</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>希岸酒店（临沂商城会展中心汽车站店）</t>
+          <t>白玉兰商务酒店（临沂大学育才路店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>希岸酒店(临沂商城会展中心汽车站店)</t>
+          <t>白玉兰酒店(临沂兰山区育才路店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>95</v>
       </c>
       <c r="I9" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1343,13 +1343,13 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P9" t="n">
         <v>30</v>
@@ -1395,29 +1395,29 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7094979881469118501</t>
+          <t>7391791030544435234</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（临沂大学育才路店）</t>
+          <t>白玉兰商务酒店（临沂罗庄区政府双月园路店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>白玉兰酒店(临沂兰山区育才路店)</t>
+          <t>白玉兰酒店(临沂罗庄区政府双月园路店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>95</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1431,13 +1431,13 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
+        <v>20</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30</v>
+      </c>
+      <c r="O10" t="n">
         <v>25</v>
-      </c>
-      <c r="N10" t="n">
-        <v>30</v>
-      </c>
-      <c r="O10" t="n">
-        <v>20</v>
       </c>
       <c r="P10" t="n">
         <v>30</v>
@@ -1483,29 +1483,29 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>7391791030544435234</t>
+          <t>7133759317631502375</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（临沂罗庄区政府双月园路店）</t>
+          <t>维也纳3好酒店（临沂大学国际博览中心商城店）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>白玉兰酒店(临沂罗庄区政府双月园路店)</t>
+          <t>维也纳3好酒店(临沂大学国际博览中心商城店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>95</v>
       </c>
       <c r="I11" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N11" t="n">
         <v>30</v>
@@ -1531,7 +1531,7 @@
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
@@ -1571,22 +1571,22 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7133759317631502375</t>
+          <t>6996515890892113928</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（临沂大学国际博览中心商城店）</t>
+          <t>维也纳3好酒店（临沂莒南天桥路店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(临沂大学国际博览中心商城店)</t>
+          <t>维也纳3好酒店(临沂莒南天桥路店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1607,13 +1607,13 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P12" t="n">
         <v>30</v>
@@ -1659,33 +1659,33 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>6996515890892113928</t>
+          <t>6697091890640062471</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（临沂莒南天桥路店）</t>
+          <t>维也纳酒店（临沂蒙阴店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(临沂莒南天桥路店)</t>
+          <t>维也纳酒店(临沂蒙阴店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1695,19 +1695,19 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N13" t="n">
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R13" t="n">
         <v>30</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2099,17 +2099,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>6729405294931167240</t>
+          <t>7402857231391131657</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>维也纳酒店（临沂河东经开区启阳国际机场店）</t>
+          <t>锦江之星（临沂琅琊景区大剧院酒店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>维也纳酒店(临沂河东经开区启阳国际机场店)</t>
+          <t>锦江之星酒店(临沂北城新区大剧院店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2121,7 +2121,7 @@
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2141,13 +2141,13 @@
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2187,17 +2187,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7402857231391131657</t>
+          <t>7509729755424360486</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>锦江之星（临沂琅琊景区大剧院酒店）</t>
+          <t>IU酒店(临沂火车站万象汇店)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>锦江之星酒店(临沂北城新区大剧院店)</t>
+          <t>IU酒店(临沂火车站万象汇店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2206,14 +2206,14 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2223,19 +2223,19 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2275,17 +2275,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7509729755424360486</t>
+          <t>7465205098587621417</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IU酒店(临沂火车站万象汇店)</t>
+          <t>临沂泰盛广场王羲之故居丽柏酒店</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IU酒店(临沂火车站万象汇店)</t>
+          <t>临沂泰盛广场王羲之故居丽柏酒店</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I20" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
@@ -2323,7 +2323,7 @@
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2363,22 +2363,22 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7465205098587621417</t>
+          <t>7038490299923957768</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>临沂泰盛广场王羲之故居丽柏酒店</t>
+          <t>白玉兰（商务）酒店临沂蒙阴云蒙路店</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>临沂泰盛广场王羲之故居丽柏酒店</t>
+          <t>白玉兰酒店(蒙阴云蒙路店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2399,13 +2399,13 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
+        <v>30</v>
+      </c>
+      <c r="N21" t="n">
+        <v>30</v>
+      </c>
+      <c r="O21" t="n">
         <v>25</v>
-      </c>
-      <c r="N21" t="n">
-        <v>30</v>
-      </c>
-      <c r="O21" t="n">
-        <v>30</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
@@ -2451,17 +2451,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7038490299923957768</t>
+          <t>7081605630280239116</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>白玉兰（商务）酒店临沂蒙阴云蒙路店</t>
+          <t>维也纳国际酒店（5.0临沂大学奥体中心店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>白玉兰酒店(蒙阴云蒙路店)</t>
+          <t>维也纳国际酒店(临沂大学奥体中心店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2473,11 +2473,11 @@
         <v>105</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2487,13 +2487,13 @@
         <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N22" t="n">
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
@@ -2539,17 +2539,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7081605630280239116</t>
+          <t>7178291053747767334</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（5.0临沂大学奥体中心店）</t>
+          <t>维也纳酒店（5.0临沂琅琊古城吾悦广场店）</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(临沂大学奥体中心店)</t>
+          <t>维也纳酒店(临沂琅琊古城河东吾悦广场店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2561,11 +2561,11 @@
         <v>105</v>
       </c>
       <c r="I23" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2575,13 +2575,13 @@
         <v>10</v>
       </c>
       <c r="M23" t="n">
+        <v>30</v>
+      </c>
+      <c r="N23" t="n">
+        <v>30</v>
+      </c>
+      <c r="O23" t="n">
         <v>25</v>
-      </c>
-      <c r="N23" t="n">
-        <v>30</v>
-      </c>
-      <c r="O23" t="n">
-        <v>30</v>
       </c>
       <c r="P23" t="n">
         <v>30</v>
@@ -2627,17 +2627,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7366484669245687819</t>
+          <t>6729405294931167240</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>锦江之星(临沂国际机场吾悦广场店)</t>
+          <t>维也纳酒店（临沂河东经开区启阳国际机场店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>锦江之星(临沂国际机场吾悦广场店)</t>
+          <t>维也纳酒店(临沂河东经开区启阳国际机场店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2649,11 +2649,11 @@
         <v>105</v>
       </c>
       <c r="I24" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2663,7 +2663,7 @@
         <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N24" t="n">
         <v>30</v>
@@ -2675,7 +2675,7 @@
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2715,17 +2715,17 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>6614031669881997326</t>
+          <t>7366484669245687819</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>锦江之星品尚（临沂北站琅琊古城酒店）</t>
+          <t>锦江之星(临沂国际机场吾悦广场店)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>锦江之星品尚酒店(临沂市政府天津路店)</t>
+          <t>锦江之星(临沂国际机场吾悦广场店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2737,11 +2737,11 @@
         <v>105</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2751,13 +2751,13 @@
         <v>10</v>
       </c>
       <c r="M25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N25" t="n">
         <v>30</v>
       </c>
       <c r="O25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P25" t="n">
         <v>30</v>
@@ -2803,17 +2803,17 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>6601143054076217357</t>
+          <t>6614031669881997326</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>锦江之星（临沂国际会展中心沂河路酒店）</t>
+          <t>锦江之星品尚（临沂北站琅琊古城酒店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>锦江之星酒店(临沂国际会展中心沂河路店)</t>
+          <t>锦江之星品尚酒店(临沂市政府天津路店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2845,13 +2845,13 @@
         <v>30</v>
       </c>
       <c r="O26" t="n">
+        <v>20</v>
+      </c>
+      <c r="P26" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q26" t="n">
         <v>25</v>
-      </c>
-      <c r="P26" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>20</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
@@ -2891,17 +2891,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>6601143739723286535</t>
+          <t>6601143054076217357</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>锦江之星（临沂罗庄店）</t>
+          <t>锦江之星（临沂国际会展中心沂河路酒店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>锦江之星(临沂罗庄店)</t>
+          <t>锦江之星酒店(临沂国际会展中心沂河路店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2979,22 +2979,22 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7050096820748060686</t>
+          <t>6601143739723286535</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>非繁城品酒店（沂水沂蒙山路恒茂广场店）</t>
+          <t>锦江之星（临沂罗庄店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>非繁城品酒店(沂水沂蒙山路店)</t>
+          <t>锦江之星(临沂罗庄店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -3015,7 +3015,7 @@
         <v>10</v>
       </c>
       <c r="M28" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N28" t="n">
         <v>30</v>
@@ -3027,7 +3027,7 @@
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
@@ -3067,22 +3067,22 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7278635894016329767</t>
+          <t>7050096820748060686</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>麗枫酒店(临沂泰盛广场万象汇酒店)</t>
+          <t>非繁城品酒店（沂水沂蒙山路恒茂广场店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>麗枫酒店(临沂泰盛广场万象汇店)</t>
+          <t>非繁城品酒店(沂水沂蒙山路店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3103,13 +3103,13 @@
         <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N29" t="n">
         <v>30</v>
       </c>
       <c r="O29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P29" t="n">
         <v>30</v>
@@ -3155,17 +3155,17 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7232165425386096698</t>
+          <t>7278635894016329767</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>麗枫酒店（临沂市政府琅琊奥体中心店）</t>
+          <t>麗枫酒店(临沂泰盛广场万象汇酒店)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>麗枫酒店(临沂市政府五洲湖武汉路店)</t>
+          <t>麗枫酒店(临沂泰盛广场万象汇店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3197,13 +3197,13 @@
         <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P30" t="n">
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3243,17 +3243,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>6601197158039291911</t>
+          <t>7232165425386096698</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>麗枫酒店（沂水万德广场店）</t>
+          <t>麗枫酒店（临沂市政府琅琊奥体中心店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>麗枫酒店(沂水万德广场店)</t>
+          <t>麗枫酒店(临沂市政府五洲湖武汉路店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3265,11 +3265,11 @@
         <v>105</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -3285,13 +3285,13 @@
         <v>30</v>
       </c>
       <c r="O31" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P31" t="n">
         <v>30</v>
       </c>
       <c r="Q31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R31" t="n">
         <v>30</v>
@@ -3331,29 +3331,29 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>6938253570235959304</t>
+          <t>6601197158039291911</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（山东临沂水开先国际店）</t>
+          <t>麗枫酒店（沂水万德广场店）</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(沂水开先国际店)</t>
+          <t>麗枫酒店(沂水万德广场店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>30</v>
       </c>
       <c r="O32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P32" t="n">
         <v>30</v>
@@ -3419,29 +3419,29 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>7178291053747767334</t>
+          <t>6938253570235959304</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0临沂琅琊古城吾悦广场店）</t>
+          <t>维也纳国际酒店（山东临沂水开先国际店）</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>维也纳酒店(临沂琅琊古城河东吾悦广场店)</t>
+          <t>维也纳国际酒店(沂水开先国际店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>110</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3507,17 +3507,17 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>7422600130257225762</t>
+          <t>7445268185810470952</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>锦江之星酒店（临沂商城中心大学城店）</t>
+          <t>维也纳酒店（临沂大学汽车站店）</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>锦江之星酒店(临沂商城中心大学城店)</t>
+          <t>维也纳酒店(临沂大学汽车站店)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3529,11 +3529,11 @@
         <v>110</v>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -3543,13 +3543,13 @@
         <v>10</v>
       </c>
       <c r="M34" t="n">
+        <v>30</v>
+      </c>
+      <c r="N34" t="n">
+        <v>30</v>
+      </c>
+      <c r="O34" t="n">
         <v>25</v>
-      </c>
-      <c r="N34" t="n">
-        <v>30</v>
-      </c>
-      <c r="O34" t="n">
-        <v>30</v>
       </c>
       <c r="P34" t="n">
         <v>30</v>
@@ -3595,17 +3595,17 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>6601136869495277576</t>
+          <t>7422600130257225762</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>麗枫酒店（临沂沂南君悦购物中心店）</t>
+          <t>锦江之星酒店（临沂商城中心大学城店）</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>麗枫酒店(临沂沂南君悦购物中心店)</t>
+          <t>锦江之星酒店(临沂商城中心大学城店)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3617,11 +3617,11 @@
         <v>110</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -3631,13 +3631,13 @@
         <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N35" t="n">
         <v>30</v>
       </c>
       <c r="O35" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P35" t="n">
         <v>30</v>
@@ -3683,17 +3683,17 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>7445268185810470952</t>
+          <t>6601136869495277576</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>维也纳酒店（临沂大学汽车站店）</t>
+          <t>麗枫酒店（临沂沂南君悦购物中心店）</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>维也纳酒店(临沂大学汽车站店)</t>
+          <t>麗枫酒店(临沂沂南君悦购物中心店)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3702,14 +3702,14 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>提质量</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -3731,7 +3731,7 @@
         <v>30</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="R36" t="n">
         <v>30</v>
